--- a/Mapping_Strategien.xlsx
+++ b/Mapping_Strategien.xlsx
@@ -1242,7 +1242,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>FFPB Strategie 30</t>
+          <t>Portfolioverwaltung 30</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>FFPB Strategie 70</t>
+          <t>Portfolioverwaltung 70</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>FFPB Strategie 100</t>
+          <t>Portfolioverwaltung 100</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
